--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>28/08 18:20</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>28/08 18:15</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/08 23:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>150</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>150</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>29/08 17:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>27/08 16:10</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F15" t="n">
+        <v>1.85</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/08 17:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>01/09 00:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>31/08 20:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>55</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>30/08 21:10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>31/08 00:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>55</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>28/08 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>27/08 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>40</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>29/08 22:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>31/08 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45896.07055800094</v>
+        <v>45896.07055799769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – LausanneLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+170%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45896.12794787024</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Luleå HF –</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Luleå HF – ZugEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+159%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45896.12794787024</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Kometa </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno – Brynas IFLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45896.12794787024</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Shintaro M</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Shintaro Mochizuki – Alex De MinaurUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+72,9%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45896.12794787024</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>175</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45896.12794787024</v>
+        <v>45896.12794787037</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>150</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45896.12794787024</v>
+        <v>45896.12794787037</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>140</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45896.12794787024</v>
+        <v>45896.12794787037</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>90</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45896.12794787024</v>
+        <v>45896.12794787037</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 7.5 - tirs2e équipe | Fiorentina</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fiorentina – FC Polissya ZhytomyrLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28/08 18:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>53,3%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+54,6%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45896.18493164567</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CA Banfield – CA TigreLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>29/08 22:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45896.18493164567</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Lorenzo – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>30/08 17:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45896.18493164567</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F31" t="n">
+        <v>2.9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45896.18493164567</v>
+        <v>45896.18493164352</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>29/08 22:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>50</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45896.18493164567</v>
+        <v>45896.18493164352</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>30/08 17:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>75</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,52 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45896.18493164567</v>
+        <v>45896.18493164352</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Manchester</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Manchester United WFC – PSV EindhovenLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>27/08 10:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+29,1%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45896.22262747321</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>27/08 10:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>45</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,52 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45896.22262747321</v>
+        <v>45896.22262747685</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 7.5 - tir cadré | Valence – </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Valence – GetafeEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>29/08 19:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+21,3%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45896.2714932092</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>29/08 19:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.35</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,142 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45896.2714932092</v>
+        <v>45896.27149320602</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | N.Djokovic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N.Djokovic – Z.SvajdaATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>27/08 15:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+31,4%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45896.30581089229</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(18:0)P | Belgique –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Belgique – FranceBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>X(18:0)P</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+21,2%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45896.30581089229</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Oxford Uni</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oxford United – BrightonEFL Cup</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+17,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45896.30581089229</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>27/08 15:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45896.30581089229</v>
+        <v>45896.3058108912</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
+      <c r="F37" t="n">
+        <v>18.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45896.30581089229</v>
+        <v>45896.3058108912</v>
       </c>
     </row>
     <row r="38">
@@ -2057,23 +2053,336 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>60</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+17,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45896.3058108912</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Gorniczy Klub Sportowy TychyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29/08 18:20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+212%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Belfast Gi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Belfast Giants – KalPaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28/08 18:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+211%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Storhamar </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Storhamar – BerlinLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | SV Wehen –</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SV Wehen – Bayern MunichCoupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+22,7%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Grenade – </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Grenade – MirandesLaLiga2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/08 19:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+17,2%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45896.30581089229</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Mlada B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FK Mlada Boleslav – Slavia PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>30/08 18:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+16,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45896.35310736873</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Twente (F)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Twente (F) – ZFK Crvena Zvezda (F)Europe - Ligue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>27/08 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45896.35310736873</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>200</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="42">
@@ -2231,10 +2225,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>65</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2247,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="43">
@@ -2276,10 +2268,8 @@
           <t>31/08 19:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2292,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="44">
@@ -2321,10 +2311,8 @@
           <t>30/08 18:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2337,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
       </c>
     </row>
     <row r="45">
@@ -2366,10 +2354,8 @@
           <t>27/08 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>25</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2382,7 +2368,97 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45896.35310736873</v>
+        <v>45896.35310737268</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Lulea Hock</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lulea Hockey – EV ZougInternational - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+71,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45896.39107174669</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Copenhague</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Copenhague – FC BâleEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+29,2%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45896.39107174669</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>101</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45896.39107174669</v>
+        <v>45896.39107174768</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.8</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,142 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45896.39107174669</v>
+        <v>45896.39107174768</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 14.5 - tirs1re équipe | FC Copenha</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FC Copenhague – FC BâleLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+29,9%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45896.43194221486</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 28.5 - tirs | Club Bruge</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Club Bruges – RangersLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>44,4%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+19,9%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45896.43194221486</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Bulgarie –</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bulgarie – EspagneCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>04/09 18:45</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+17,4%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45896.43194221486</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.95</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45896.43194221486</v>
+        <v>45896.43194221065</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.7</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45896.43194221486</v>
+        <v>45896.43194221065</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45896.43194221486</v>
+        <v>45896.43194221065</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X(14:0)P | Monténégro</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Monténégro – AllemagneChampionnat d’Europe de basket</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>X(14:0)P</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>27/08 13:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45896.47090863621</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs2e équipe | Copenhague</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Copenhague – FC BâleEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45896.47090863621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>27/08 13:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>19</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45896.47090863621</v>
+        <v>45896.47090863426</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F52" t="n">
+        <v>3.2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,547 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45896.47090863621</v>
+        <v>45896.47090863426</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Spar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>KAC – Sparta PragueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>28/08 18:20</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Grenoble –</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Grenoble – BernEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>28/08 18:15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frolunda –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Frolunda – HC Bolzano-Bozen FoxesLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Fischtown PinguinsInternational - Ligue des Champions stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>29/08 17:45</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+67,8%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mountfield HK – OdenseBulldogInternational - ChampionsLeague</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+50,9%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Italie – E</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Italie – EstonieCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>05/09 18:45</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+28,2%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – Brann-BergenEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>27/08 16:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+18,3%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Grèce – Bi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Grèce – BiélorussieCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05/09 18:45</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,60%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+17,2%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Internacional – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>31/08 23:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Guarani – </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Guarani – Club General Caballero JLMPrimera Division</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>31/08 21:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X(13:0)P | Suède – Fi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Suède – FinlandeChampionnat d’Europe de basket A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>X(13:0)P</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/08 17:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45896.52999820029</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 0.5 - break1er participant | Lloyd Harr</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Lloyd Harris – Taylor FritzUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 0.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>27/08 17:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>51,4%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+13,0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45896.52999820029</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>28/08 18:20</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>175</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>28/08 18:15</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>175</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>175</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="56">
@@ -2833,10 +2827,8 @@
           <t>29/08 17:45</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>101</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2849,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="57">
@@ -2878,10 +2870,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>100</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2894,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="58">
@@ -2923,10 +2913,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>55</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2939,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="59">
@@ -2968,10 +2956,8 @@
           <t>27/08 16:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F59" t="n">
+        <v>3.1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2984,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="60">
@@ -3013,10 +2999,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3029,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="61">
@@ -3058,10 +3042,8 @@
           <t>31/08 23:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3074,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="62">
@@ -3103,10 +3085,8 @@
           <t>31/08 21:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>45</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3119,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="63">
@@ -3148,10 +3128,8 @@
           <t>27/08 17:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>20</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3164,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
       </c>
     </row>
     <row r="64">
@@ -3193,10 +3171,8 @@
           <t>27/08 17:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2.2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3209,7 +3185,142 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45896.52999820029</v>
+        <v>45896.52999820602</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 13.5 - tirs2e équipe | KuPS Kuopi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KuPS Kuopio – FC MidtjyllandLigue Europa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+30,9%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45896.56268555808</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 11.5 - tirs2e équipe | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – SK BrannLigue Europa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>27/08 16:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+25,5%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45896.56268555808</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Vizela </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FC Vizela – UD OliveirensePortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>31/08 14:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45896.56268555808</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45896.56268555808</v>
+        <v>45896.56268555555</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>27/08 16:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45896.56268555808</v>
+        <v>45896.56268555555</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>31/08 14:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>50</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45896.56268555808</v>
+        <v>45896.56268555555</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 21-2- se qualifie | Everton – </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Everton – Mansfield Town385076e7 Angleterre. EFL Cup</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45896.59778592113</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -3343,10 +3343,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
+      <c r="F68" t="n">
+        <v>9.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45896.59778592113</v>
+        <v>45896.59778592593</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,6 +3360,231 @@
         <v>45896.59778592593</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Angleterre</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Angleterre – AndorreCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>06/09 16:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+35,6%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45896.68549351824</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 12.5 - tirs2e équipe | Club Bruge</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Club Bruges – RangersLigue des Champions (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>42,3%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+22,7%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45896.68549351824</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs1re équipe | Copenhague</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Copenhague – FC BâleEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45896.68549351824</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Felgueiras</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932 – Lusitania FC LourosaPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>30/08 13:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45896.68549351824</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 22.5 - tirs | Arda FK – </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Arda FK – Rakow CzestochowaEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>28/08 18:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45896.68549351824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>75</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45896.68549351824</v>
+        <v>45896.68549351852</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45896.68549351824</v>
+        <v>45896.68549351852</v>
       </c>
     </row>
     <row r="71">
@@ -3476,10 +3472,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.7</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3492,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45896.68549351824</v>
+        <v>45896.68549351852</v>
       </c>
     </row>
     <row r="72">
@@ -3521,10 +3515,8 @@
           <t>30/08 13:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>40</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3537,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45896.68549351824</v>
+        <v>45896.68549351852</v>
       </c>
     </row>
     <row r="73">
@@ -3566,10 +3558,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.8</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3582,7 +3572,52 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45896.68549351824</v>
+        <v>45896.68549351852</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Liechtenst</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Liechtenstein – BelgiqueCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>04/09 18:45</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+33,7%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45896.72137731847</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,10 +3601,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>75</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,97 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45896.72137731847</v>
+        <v>45896.72137731482</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | ERC Ingols</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt – Ilves TampereLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>28/08 17:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+128%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45896.77071679741</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fulham – B</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fulham – Bristol CityEFL Cup</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45896.77071679741</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>150</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45896.77071679741</v>
+        <v>45896.77071679398</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>60</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,52 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45896.77071679741</v>
+        <v>45896.77071679398</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Sporting L</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon B – FC Pacos FerreiraPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>31/08 10:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45896.80398064322</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>31/08 10:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>40</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,52 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45896.80398064322</v>
+        <v>45896.80398064815</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Tristan Bo</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tristan Boyer – Andrey RublevUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2,00%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+40,3%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45896.84967673668</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -3773,10 +3773,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>70</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3789,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45896.84967673668</v>
+        <v>45896.84967673611</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,6 +3790,51 @@
         <v>45896.84967673611</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Ben Shelto</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ben Shelton – Pablo Carreno-BustaUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>28/08 00:10</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+17,6%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45896.93016209216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-27.xlsx
+++ b/data/valuebets_database_2025-08-27.xlsx
@@ -3816,10 +3816,8 @@
           <t>28/08 00:10</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>55</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3832,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45896.93016209216</v>
+        <v>45896.9301620949</v>
       </c>
     </row>
   </sheetData>
